--- a/SGC-CKN/Excel/9a0de2ac-1a8b-4b33-81cc-646e97c8dfcf_Cọc_khoan_nhồi_đại_trà_P7-164_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/9a0de2ac-1a8b-4b33-81cc-646e97c8dfcf_Cọc_khoan_nhồi_đại_trà_P7-164_D800_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:04 21/03/2026</t>
+    <t>05:04 21/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -213,7 +213,7 @@
 21/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">03:10
+    <t xml:space="preserve">03:00
 21/03/2026</t>
   </si>
   <si>
@@ -223,7 +223,11 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">11:04
+    <t xml:space="preserve">03:03
+21/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:04
 21/03/2026</t>
   </si>
   <si>
@@ -1353,16 +1357,16 @@
         <v>-12</v>
       </c>
       <c r="G14" s="16">
-        <v>-20.2</v>
+        <v>-20</v>
       </c>
       <c r="H14" s="16">
         <v>0.6</v>
       </c>
       <c r="I14" s="16">
-        <v>8.2</v>
+        <v>8</v>
       </c>
       <c r="J14" s="8">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1385,19 +1389,19 @@
         <v>46</v>
       </c>
       <c r="F15" s="19">
-        <v>-20.2</v>
+        <v>-20</v>
       </c>
       <c r="G15" s="19">
-        <v>-24.5</v>
+        <v>-24</v>
       </c>
       <c r="H15" s="19">
         <v>0.47</v>
       </c>
       <c r="I15" s="19">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="8">
-        <v>9.21</v>
+        <v>8.57</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1420,10 +1424,10 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>-24.5</v>
+        <v>-24</v>
       </c>
       <c r="G16" s="22">
-        <v>-28.5</v>
+        <v>-28</v>
       </c>
       <c r="H16" s="22">
         <v>0.83</v>
@@ -1455,10 +1459,10 @@
         <v>53</v>
       </c>
       <c r="F17" s="25">
-        <v>-28.5</v>
+        <v>-28</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.5</v>
+        <v>-38</v>
       </c>
       <c r="H17" s="25">
         <v>0.33</v>
@@ -1490,10 +1494,10 @@
         <v>57</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.5</v>
+        <v>-38</v>
       </c>
       <c r="G18" s="28">
-        <v>-41</v>
+        <v>-40.5</v>
       </c>
       <c r="H18" s="28">
         <v>0.33</v>
@@ -1525,19 +1529,19 @@
         <v>61</v>
       </c>
       <c r="F19" s="31">
-        <v>-41</v>
+        <v>-40.5</v>
       </c>
       <c r="G19" s="31">
-        <v>-42.5</v>
+        <v>-41.57</v>
       </c>
       <c r="H19" s="31">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="I19" s="31">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="J19" s="34">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1554,25 +1558,25 @@
         <v>63</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" s="35">
-        <v>-42.5</v>
+        <v>-41.57</v>
       </c>
       <c r="G20" s="35">
-        <v>-46.48</v>
+        <v>-44.98</v>
       </c>
       <c r="H20" s="35">
-        <v>7.9</v>
+        <v>0.02</v>
       </c>
       <c r="I20" s="35">
-        <v>4</v>
-      </c>
-      <c r="J20" s="34">
-        <v>0.5</v>
+        <v>3.41</v>
+      </c>
+      <c r="J20" s="8">
+        <v>204.6</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1580,7 +1584,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1686,31 +1690,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1817,16 +1821,16 @@
         <v>-12</v>
       </c>
       <c r="F5" s="16">
-        <v>-20.2</v>
+        <v>-20</v>
       </c>
       <c r="G5" s="16">
         <v>0.6</v>
       </c>
       <c r="H5" s="16">
-        <v>8.2</v>
+        <v>8</v>
       </c>
       <c r="I5" s="8">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1843,19 +1847,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-20.2</v>
+        <v>-20</v>
       </c>
       <c r="F6" s="19">
-        <v>-24.5</v>
+        <v>-24</v>
       </c>
       <c r="G6" s="19">
         <v>0.47</v>
       </c>
       <c r="H6" s="19">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="8">
-        <v>9.21</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1872,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-24.5</v>
+        <v>-24</v>
       </c>
       <c r="F7" s="22">
-        <v>-28.5</v>
+        <v>-28</v>
       </c>
       <c r="G7" s="22">
         <v>0.83</v>
@@ -1901,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-28.5</v>
+        <v>-28</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.5</v>
+        <v>-38</v>
       </c>
       <c r="G8" s="25">
         <v>0.33</v>
@@ -1930,10 +1934,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.5</v>
+        <v>-38</v>
       </c>
       <c r="F9" s="28">
-        <v>-41</v>
+        <v>-40.5</v>
       </c>
       <c r="G9" s="28">
         <v>0.33</v>
@@ -1959,19 +1963,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-41</v>
+        <v>-40.5</v>
       </c>
       <c r="F10" s="31">
-        <v>-42.5</v>
+        <v>-41.57</v>
       </c>
       <c r="G10" s="31">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="H10" s="31">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="I10" s="34">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1988,24 +1992,24 @@
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-42.5</v>
+        <v>-41.57</v>
       </c>
       <c r="F11" s="35">
-        <v>-46.48</v>
+        <v>-44.98</v>
       </c>
       <c r="G11" s="35">
-        <v>7.9</v>
+        <v>0.02</v>
       </c>
       <c r="H11" s="35">
-        <v>4</v>
-      </c>
-      <c r="I11" s="34">
-        <v>0.51</v>
+        <v>3.41</v>
+      </c>
+      <c r="I11" s="8">
+        <v>204.6</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2020,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-46.48</v>
+        <v>-44.98</v>
       </c>
       <c r="G12" s="40">
-        <v>15.22</v>
+        <v>7.17</v>
       </c>
       <c r="H12" s="40">
-        <v>46.5</v>
+        <v>44.98</v>
       </c>
       <c r="I12" s="40">
-        <v>3.06</v>
+        <v>6.28</v>
       </c>
     </row>
   </sheetData>
